--- a/SHINHWA_QMS_WORKFLOW/12_OUTPUT/REPORTS/개당원가분석표_R2_20261028.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/12_OUTPUT/REPORTS/개당원가분석표_R2_20261028.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="519">
   <si>
     <r>
       <rPr>
@@ -4199,6 +4199,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">확인완료</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -4254,74 +4257,36 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">안 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">90%=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">검토보고서 예시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실적 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OEE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 교체 필요 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">| </t>
+      <t xml:space="preserve">안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인된 실제 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OEE | </t>
     </r>
     <r>
       <rPr>
@@ -17887,7 +17852,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -18076,6 +18041,10 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
     <xf numFmtId="174" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
@@ -18085,6 +18054,10 @@
       <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -18592,7 +18565,7 @@
       </c>
       <c r="B6" s="10" t="str">
         <f aca="false">COUNTIF(입력!G6:G53,"확인완료")&amp;" / 44 항목 확인완료"</f>
-        <v>0 / 44 항목 확인완료</v>
+        <v>3 / 44 항목 확인완료</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -18803,15 +18776,15 @@
       </c>
       <c r="D17" s="19" t="n">
         <f aca="false">입력!D35/입력!D36</f>
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="E17" s="17" t="n">
         <f aca="false">D17-C17</f>
-        <v>0</v>
+        <v>-114</v>
       </c>
       <c r="F17" s="18" t="n">
         <f aca="false">IF(C17=0,"-",D17/C17-1)</f>
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>33</v>
@@ -18855,15 +18828,15 @@
       </c>
       <c r="D19" s="21" t="n">
         <f aca="false">D14+D15+D16+D17+D18</f>
-        <v>2339</v>
+        <v>2225</v>
       </c>
       <c r="E19" s="21" t="n">
         <f aca="false">D19-C19</f>
-        <v>0</v>
+        <v>-114</v>
       </c>
       <c r="F19" s="22" t="n">
         <f aca="false">IF(C19=0,"-",D19/C19-1)</f>
-        <v>0</v>
+        <v>-0.0487387772552372</v>
       </c>
       <c r="G19" s="8"/>
     </row>
@@ -18880,15 +18853,15 @@
       </c>
       <c r="D20" s="24" t="n">
         <f aca="false">D13+D19</f>
-        <v>5249.75922242965</v>
+        <v>5135.75922242965</v>
       </c>
       <c r="E20" s="24" t="n">
         <f aca="false">D20-C20</f>
-        <v>0</v>
+        <v>-114</v>
       </c>
       <c r="F20" s="25" t="n">
         <f aca="false">IF(C20=0,"-",D20/C20-1)</f>
-        <v>0</v>
+        <v>-0.0217152816290953</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>37</v>
@@ -18918,15 +18891,15 @@
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">CT계산!D31</f>
-        <v>232.727272727273</v>
+        <v>344.727272727273</v>
       </c>
       <c r="E22" s="17" t="n">
         <f aca="false">D22-C22</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="F22" s="18" t="n">
         <f aca="false">IF(C22=0,"-",D22/C22-1)</f>
-        <v>0</v>
+        <v>0.48125</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>40</v>
@@ -18945,15 +18918,15 @@
       </c>
       <c r="D23" s="19" t="n">
         <f aca="false">CT계산!D32</f>
-        <v>232.727272727273</v>
+        <v>275.781818181818</v>
       </c>
       <c r="E23" s="17" t="n">
         <f aca="false">D23-C23</f>
-        <v>0</v>
+        <v>43.0545454545455</v>
       </c>
       <c r="F23" s="18" t="n">
         <f aca="false">IF(C23=0,"-",D23/C23-1)</f>
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>40</v>
@@ -18972,15 +18945,15 @@
       </c>
       <c r="D24" s="21" t="n">
         <f aca="false">D22+D23</f>
-        <v>465.454545454545</v>
+        <v>620.509090909091</v>
       </c>
       <c r="E24" s="21" t="n">
         <f aca="false">D24-C24</f>
-        <v>0</v>
+        <v>155.054545454545</v>
       </c>
       <c r="F24" s="22" t="n">
         <f aca="false">IF(C24=0,"-",D24/C24-1)</f>
-        <v>0</v>
+        <v>0.333125</v>
       </c>
       <c r="G24" s="8"/>
     </row>
@@ -19172,15 +19145,15 @@
       </c>
       <c r="D32" s="24" t="n">
         <f aca="false">D24+D31</f>
-        <v>545.454545454546</v>
+        <v>700.509090909091</v>
       </c>
       <c r="E32" s="24" t="n">
         <f aca="false">D32-C32</f>
-        <v>0</v>
+        <v>155.054545454545</v>
       </c>
       <c r="F32" s="25" t="n">
         <f aca="false">IF(C32=0,"-",D32/C32-1)</f>
-        <v>0</v>
+        <v>0.284266666666666</v>
       </c>
       <c r="G32" s="27" t="s">
         <v>51</v>
@@ -19210,15 +19183,15 @@
       </c>
       <c r="D34" s="24" t="n">
         <f aca="false">D20+D32</f>
-        <v>5795.21376788419</v>
+        <v>5836.26831333874</v>
       </c>
       <c r="E34" s="24" t="n">
         <f aca="false">D34-C34</f>
-        <v>0</v>
+        <v>41.0545454545445</v>
       </c>
       <c r="F34" s="25" t="n">
         <f aca="false">IF(C34=0,"-",D34/C34-1)</f>
-        <v>0</v>
+        <v>0.007084215888991</v>
       </c>
       <c r="G34" s="27" t="s">
         <v>54</v>
@@ -19237,15 +19210,15 @@
       </c>
       <c r="D35" s="24" t="n">
         <f aca="false">D34/(1-입력!D49)</f>
-        <v>5795.21376788419</v>
+        <v>5836.26831333874</v>
       </c>
       <c r="E35" s="24" t="n">
         <f aca="false">D35-C35</f>
-        <v>0</v>
+        <v>41.0545454545445</v>
       </c>
       <c r="F35" s="25" t="n">
         <f aca="false">IF(C35=0,"-",D35/C35-1)</f>
-        <v>0</v>
+        <v>0.007084215888991</v>
       </c>
       <c r="G35" s="26" t="s">
         <v>56</v>
@@ -19264,15 +19237,15 @@
       </c>
       <c r="D36" s="17" t="n">
         <f aca="false">D35*입력!D51</f>
-        <v>637.473514467261</v>
+        <v>641.989514467261</v>
       </c>
       <c r="E36" s="17" t="n">
         <f aca="false">D36-C36</f>
-        <v>0</v>
+        <v>4.51599999999985</v>
       </c>
       <c r="F36" s="18" t="n">
         <f aca="false">IF(C36=0,"-",D36/C36-1)</f>
-        <v>0</v>
+        <v>0.007084215888991</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>58</v>
@@ -19291,15 +19264,15 @@
       </c>
       <c r="D37" s="24" t="n">
         <f aca="false">D35+D36</f>
-        <v>6432.68728235145</v>
+        <v>6478.257827806</v>
       </c>
       <c r="E37" s="24" t="n">
         <f aca="false">D37-C37</f>
-        <v>0</v>
+        <v>45.5705454545441</v>
       </c>
       <c r="F37" s="25" t="n">
         <f aca="false">IF(C37=0,"-",D37/C37-1)</f>
-        <v>0</v>
+        <v>0.007084215888991</v>
       </c>
       <c r="G37" s="27"/>
     </row>
@@ -19316,15 +19289,15 @@
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">D37*입력!D53</f>
-        <v>643.268728235145</v>
+        <v>647.8257827806</v>
       </c>
       <c r="E38" s="17" t="n">
         <f aca="false">D38-C38</f>
-        <v>0</v>
+        <v>4.55705454545443</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">IF(C38=0,"-",D38/C38-1)</f>
-        <v>0</v>
+        <v>0.007084215888991</v>
       </c>
       <c r="G38" s="8"/>
     </row>
@@ -19341,15 +19314,15 @@
       </c>
       <c r="D39" s="17" t="n">
         <f aca="false">D37+D38</f>
-        <v>7075.9560105866</v>
+        <v>7126.0836105866</v>
       </c>
       <c r="E39" s="17" t="n">
         <f aca="false">D39-C39</f>
-        <v>0</v>
+        <v>50.1275999999989</v>
       </c>
       <c r="F39" s="18" t="n">
         <f aca="false">IF(C39=0,"-",D39/C39-1)</f>
-        <v>0</v>
+        <v>0.007084215888991</v>
       </c>
       <c r="G39" s="8"/>
     </row>
@@ -19390,15 +19363,15 @@
       </c>
       <c r="D41" s="17" t="n">
         <f aca="false">D35/(1-입력!D52)</f>
-        <v>6511.4761436901</v>
+        <v>6557.60484644802</v>
       </c>
       <c r="E41" s="17" t="n">
         <f aca="false">D41-C41</f>
-        <v>0</v>
+        <v>46.1287027579147</v>
       </c>
       <c r="F41" s="18" t="n">
         <f aca="false">IF(C41=0,"-",D41/C41-1)</f>
-        <v>0</v>
+        <v>0.007084215888991</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>66</v>
@@ -19417,15 +19390,15 @@
       </c>
       <c r="D42" s="17" t="n">
         <f aca="false">D41-D37</f>
-        <v>78.7888613386504</v>
+        <v>79.3470186420209</v>
       </c>
       <c r="E42" s="17" t="n">
         <f aca="false">D42-C42</f>
-        <v>0</v>
+        <v>0.558157303370535</v>
       </c>
       <c r="F42" s="18" t="n">
         <f aca="false">IF(C42=0,"-",D42/C42-1)</f>
-        <v>0</v>
+        <v>0.00708421588898789</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>68</v>
@@ -19455,11 +19428,11 @@
       </c>
       <c r="D44" s="18" t="n">
         <f aca="false">D20/D37</f>
-        <v>0.816106705020893</v>
+        <v>0.792768574351259</v>
       </c>
       <c r="E44" s="18" t="n">
         <f aca="false">D44-C44</f>
-        <v>0</v>
+        <v>-0.0233381306696335</v>
       </c>
       <c r="F44" s="29"/>
       <c r="G44" s="8"/>
@@ -19477,11 +19450,11 @@
       </c>
       <c r="D45" s="18" t="n">
         <f aca="false">D24/D37</f>
-        <v>0.0723577138176068</v>
+        <v>0.0957833274627848</v>
       </c>
       <c r="E45" s="18" t="n">
         <f aca="false">D45-C45</f>
-        <v>0</v>
+        <v>0.023425613645178</v>
       </c>
       <c r="F45" s="29"/>
       <c r="G45" s="8"/>
@@ -19499,11 +19472,11 @@
       </c>
       <c r="D46" s="18" t="n">
         <f aca="false">D31/D37</f>
-        <v>0.0124364820624012</v>
+        <v>0.0123489990868569</v>
       </c>
       <c r="E46" s="18" t="n">
         <f aca="false">D46-C46</f>
-        <v>0</v>
+        <v>-8.74829755442459E-005</v>
       </c>
       <c r="F46" s="29"/>
       <c r="G46" s="8"/>
@@ -19576,15 +19549,15 @@
       </c>
       <c r="D50" s="30" t="n">
         <f aca="false">D37*입력!D6</f>
-        <v>16081718.2058786</v>
+        <v>16195644.569515</v>
       </c>
       <c r="E50" s="17" t="n">
         <f aca="false">D50-C50</f>
-        <v>0</v>
+        <v>113926.363636361</v>
       </c>
       <c r="F50" s="18" t="n">
         <f aca="false">IF(C50=0,"-",D50/C50-1)</f>
-        <v>0</v>
+        <v>0.007084215888991</v>
       </c>
       <c r="G50" s="8"/>
     </row>
@@ -19626,15 +19599,15 @@
       </c>
       <c r="D52" s="30" t="n">
         <f aca="false">D37*D51</f>
-        <v>353797800.52933</v>
+        <v>356304180.52933</v>
       </c>
       <c r="E52" s="17" t="n">
         <f aca="false">D52-C52</f>
-        <v>0</v>
+        <v>2506379.99999994</v>
       </c>
       <c r="F52" s="18" t="n">
         <f aca="false">IF(C52=0,"-",D52/C52-1)</f>
-        <v>0</v>
+        <v>0.007084215888991</v>
       </c>
       <c r="G52" s="8"/>
     </row>
@@ -19651,15 +19624,15 @@
       </c>
       <c r="D53" s="30" t="n">
         <f aca="false">D36*D51</f>
-        <v>35061043.2956994</v>
+        <v>35309423.2956994</v>
       </c>
       <c r="E53" s="17" t="n">
         <f aca="false">D53-C53</f>
-        <v>0</v>
+        <v>248379.999999993</v>
       </c>
       <c r="F53" s="18" t="n">
         <f aca="false">IF(C53=0,"-",D53/C53-1)</f>
-        <v>0</v>
+        <v>0.007084215888991</v>
       </c>
       <c r="G53" s="8"/>
     </row>
@@ -19687,15 +19660,15 @@
       </c>
       <c r="D55" s="32" t="n">
         <f aca="false">CT계산!D18</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E55" s="17" t="n">
         <f aca="false">D55-C55</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="18" t="n">
         <f aca="false">IF(C55=0,"-",D55/C55-1)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>80</v>
@@ -19714,15 +19687,15 @@
       </c>
       <c r="D56" s="32" t="n">
         <f aca="false">CT계산!D28</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E56" s="17" t="n">
         <f aca="false">D56-C56</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="18" t="n">
         <f aca="false">IF(C56=0,"-",D56/C56-1)</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="G56" s="8"/>
     </row>
@@ -19739,11 +19712,11 @@
       </c>
       <c r="D57" s="33" t="n">
         <f aca="false">CT계산!D21</f>
-        <v>0.912698412698413</v>
+        <v>0.839262908228425</v>
       </c>
       <c r="E57" s="18" t="n">
         <f aca="false">D57-C57</f>
-        <v>0</v>
+        <v>-0.0734355044699874</v>
       </c>
       <c r="F57" s="29"/>
       <c r="G57" s="8"/>
@@ -20294,7 +20267,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="24.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
         <v>133</v>
       </c>
@@ -20304,25 +20277,25 @@
       <c r="C15" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="46" t="n">
-        <v>1</v>
+      <c r="D15" s="47" t="n">
+        <v>0.87</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="F15" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="G15" s="42" t="s">
         <v>134</v>
-      </c>
-      <c r="G15" s="42" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="45" t="n">
         <v>46</v>
@@ -20334,7 +20307,7 @@
         <v>111</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G16" s="42" t="s">
         <v>111</v>
@@ -20342,10 +20315,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C17" s="45" t="n">
         <v>1</v>
@@ -20363,10 +20336,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C18" s="43" t="n">
         <v>4</v>
@@ -20378,7 +20351,7 @@
         <v>111</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G18" s="42" t="s">
         <v>111</v>
@@ -20386,10 +20359,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="43" t="n">
         <v>1</v>
@@ -20401,7 +20374,7 @@
         <v>111</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G19" s="42" t="s">
         <v>111</v>
@@ -20409,7 +20382,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -20419,10 +20392,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C21" s="39" t="n">
         <v>5200</v>
@@ -20434,7 +20407,7 @@
         <v>111</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G21" s="42" t="s">
         <v>111</v>
@@ -20442,22 +20415,22 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="C22" s="47" t="n">
+        <v>152</v>
+      </c>
+      <c r="C22" s="48" t="n">
         <v>7.93</v>
       </c>
-      <c r="D22" s="47" t="n">
+      <c r="D22" s="48" t="n">
         <v>7.93</v>
       </c>
       <c r="E22" s="40" t="s">
         <v>111</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G22" s="42" t="s">
         <v>111</v>
@@ -20465,22 +20438,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="C23" s="47" t="n">
+        <v>155</v>
+      </c>
+      <c r="C23" s="48" t="n">
         <v>25.4</v>
       </c>
-      <c r="D23" s="47" t="n">
+      <c r="D23" s="48" t="n">
         <v>25.4</v>
       </c>
       <c r="E23" s="40" t="s">
         <v>111</v>
       </c>
       <c r="F23" s="41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G23" s="42" t="s">
         <v>111</v>
@@ -20488,22 +20461,22 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="C24" s="47" t="n">
+        <v>155</v>
+      </c>
+      <c r="C24" s="48" t="n">
         <v>1.24</v>
       </c>
-      <c r="D24" s="47" t="n">
+      <c r="D24" s="48" t="n">
         <v>1.24</v>
       </c>
       <c r="E24" s="40" t="s">
         <v>111</v>
       </c>
       <c r="F24" s="41" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G24" s="42" t="s">
         <v>111</v>
@@ -20511,10 +20484,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C25" s="39" t="n">
         <v>435</v>
@@ -20526,7 +20499,7 @@
         <v>111</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G25" s="42" t="s">
         <v>111</v>
@@ -20534,10 +20507,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C26" s="39" t="n">
         <v>315</v>
@@ -20549,7 +20522,7 @@
         <v>111</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G26" s="42" t="s">
         <v>111</v>
@@ -20557,7 +20530,7 @@
     </row>
     <row r="27" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>63</v>
@@ -20572,7 +20545,7 @@
         <v>111</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G27" s="42" t="s">
         <v>111</v>
@@ -20580,7 +20553,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -20590,22 +20563,22 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C29" s="48" t="n">
+        <v>166</v>
+      </c>
+      <c r="C29" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="48" t="n">
+      <c r="D29" s="49" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="40" t="s">
         <v>111</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G29" s="42" t="s">
         <v>111</v>
@@ -20613,7 +20586,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>27</v>
@@ -20628,7 +20601,7 @@
         <v>111</v>
       </c>
       <c r="F30" s="41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G30" s="42" t="s">
         <v>111</v>
@@ -20636,22 +20609,22 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C31" s="48" t="n">
+        <v>166</v>
+      </c>
+      <c r="C31" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="48" t="n">
+      <c r="D31" s="49" t="n">
         <v>2</v>
       </c>
       <c r="E31" s="40" t="s">
         <v>111</v>
       </c>
       <c r="F31" s="41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G31" s="42" t="s">
         <v>111</v>
@@ -20659,7 +20632,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>27</v>
@@ -20680,15 +20653,15 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C33" s="48" t="n">
+        <v>166</v>
+      </c>
+      <c r="C33" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="48" t="n">
+      <c r="D33" s="49" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="40" t="s">
@@ -20701,22 +20674,22 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="49" t="n">
+      <c r="C34" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="49" t="n">
+      <c r="D34" s="50" t="n">
         <v>3</v>
       </c>
       <c r="E34" s="40" t="s">
         <v>111</v>
       </c>
       <c r="F34" s="44" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G34" s="42" t="s">
         <v>111</v>
@@ -20724,7 +20697,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>27</v>
@@ -20745,7 +20718,7 @@
     </row>
     <row r="36" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>74</v>
@@ -20753,37 +20726,37 @@
       <c r="C36" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="43" t="n">
-        <v>1</v>
+      <c r="D36" s="51" t="n">
+        <v>20</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="F36" s="44" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G36" s="42" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C37" s="48" t="n">
+        <v>166</v>
+      </c>
+      <c r="C37" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="48" t="n">
+      <c r="D37" s="49" t="n">
         <v>2</v>
       </c>
       <c r="E37" s="40" t="s">
         <v>111</v>
       </c>
       <c r="F37" s="44" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G37" s="42" t="s">
         <v>111</v>
@@ -20791,15 +20764,15 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="49" t="n">
+      <c r="C38" s="50" t="n">
         <v>8</v>
       </c>
-      <c r="D38" s="49" t="n">
+      <c r="D38" s="50" t="n">
         <v>8</v>
       </c>
       <c r="E38" s="40" t="s">
@@ -20812,7 +20785,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -20821,11 +20794,11 @@
       <c r="F39" s="14"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="50" t="s">
-        <v>182</v>
+      <c r="A40" s="52" t="s">
+        <v>183</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C40" s="39" t="n">
         <v>3200000</v>
@@ -20837,18 +20810,18 @@
         <v>111</v>
       </c>
       <c r="F40" s="41" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G40" s="42" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="50" t="s">
-        <v>185</v>
+      <c r="A41" s="52" t="s">
+        <v>186</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C41" s="39" t="n">
         <v>0</v>
@@ -20860,7 +20833,7 @@
         <v>111</v>
       </c>
       <c r="F41" s="41" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G41" s="42" t="s">
         <v>111</v>
@@ -20868,7 +20841,7 @@
     </row>
     <row r="42" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>63</v>
@@ -20876,17 +20849,17 @@
       <c r="C42" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="46" t="n">
-        <v>0</v>
+      <c r="D42" s="47" t="n">
+        <v>0.185</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="F42" s="44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G42" s="42" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20906,7 +20879,7 @@
         <v>111</v>
       </c>
       <c r="F43" s="41" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G43" s="42" t="s">
         <v>111</v>
@@ -20914,22 +20887,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="49" t="n">
+      <c r="C44" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="49" t="n">
+      <c r="D44" s="50" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="40" t="s">
         <v>111</v>
       </c>
       <c r="F44" s="41" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G44" s="42" t="s">
         <v>111</v>
@@ -20942,17 +20915,17 @@
       <c r="B45" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="49" t="n">
+      <c r="C45" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D45" s="49" t="n">
+      <c r="D45" s="50" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="40" t="s">
         <v>111</v>
       </c>
       <c r="F45" s="41" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G45" s="42" t="s">
         <v>111</v>
@@ -20965,10 +20938,10 @@
       <c r="B46" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="49" t="n">
+      <c r="C46" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="49" t="n">
+      <c r="D46" s="50" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="40" t="s">
@@ -20986,10 +20959,10 @@
       <c r="B47" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="49" t="n">
+      <c r="C47" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="49" t="n">
+      <c r="D47" s="50" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="40" t="s">
@@ -21002,22 +20975,22 @@
     </row>
     <row r="48" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="49" t="n">
+      <c r="C48" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="49" t="n">
+      <c r="D48" s="50" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="40" t="s">
         <v>111</v>
       </c>
       <c r="F48" s="44" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G48" s="42" t="s">
         <v>111</v>
@@ -21025,7 +20998,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>63</v>
@@ -21040,7 +21013,7 @@
         <v>111</v>
       </c>
       <c r="F49" s="41" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G49" s="42" t="s">
         <v>111</v>
@@ -21048,7 +21021,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -21058,7 +21031,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>63</v>
@@ -21073,7 +21046,7 @@
         <v>111</v>
       </c>
       <c r="F51" s="44" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G51" s="42" t="s">
         <v>111</v>
@@ -21081,7 +21054,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>63</v>
@@ -21096,7 +21069,7 @@
         <v>111</v>
       </c>
       <c r="F52" s="41" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G52" s="42" t="s">
         <v>111</v>
@@ -21104,7 +21077,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>63</v>
@@ -21116,10 +21089,10 @@
         <v>0.1</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F53" s="41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G53" s="42" t="s">
         <v>111</v>
@@ -21130,13 +21103,13 @@
         <v>11</v>
       </c>
       <c r="B54" s="8"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="51"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="53"/>
       <c r="E54" s="40" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F54" s="41" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -21361,18 +21334,18 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="52" t="s">
-        <v>207</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
+      <c r="A1" s="54" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -21395,12 +21368,12 @@
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -21410,7 +21383,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>125</v>
@@ -21424,50 +21397,50 @@
         <v>660</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="53" t="n">
+      <c r="C7" s="55" t="n">
         <f aca="false">ROUNDDOWN((입력!C9-입력!C8)/입력!C10,0)</f>
         <v>5</v>
       </c>
-      <c r="D7" s="53" t="n">
+      <c r="D7" s="55" t="n">
         <f aca="false">ROUNDDOWN((입력!D9-입력!D8)/입력!D10,0)</f>
         <v>5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="53" t="n">
+      <c r="C8" s="55" t="n">
         <f aca="false">MAX(0,C7-입력!C12)</f>
         <v>5</v>
       </c>
-      <c r="D8" s="53" t="n">
+      <c r="D8" s="55" t="n">
         <f aca="false">MAX(0,D7-입력!D12)</f>
         <v>5</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>125</v>
@@ -21481,12 +21454,12 @@
         <v>75</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>125</v>
@@ -21500,12 +21473,12 @@
         <v>60</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>125</v>
@@ -21519,15 +21492,15 @@
         <v>525</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C12" s="30" t="n">
         <f aca="false">C11*60</f>
@@ -21541,45 +21514,45 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="54" t="n">
+        <v>137</v>
+      </c>
+      <c r="C13" s="56" t="n">
         <f aca="false">C12/입력!C6</f>
         <v>12.6</v>
       </c>
-      <c r="D13" s="54" t="n">
+      <c r="D13" s="56" t="n">
         <f aca="false">D12/입력!D6</f>
         <v>12.6</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="50" t="s">
-        <v>226</v>
+      <c r="A14" s="52" t="s">
+        <v>227</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="54" t="n">
+        <v>137</v>
+      </c>
+      <c r="C14" s="56" t="n">
         <f aca="false">C13*입력!C15</f>
         <v>12.6</v>
       </c>
-      <c r="D14" s="54" t="n">
+      <c r="D14" s="56" t="n">
         <f aca="false">D13*입력!D15</f>
-        <v>12.6</v>
+        <v>10.962</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -21589,100 +21562,100 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="55" t="n">
+      <c r="C16" s="57" t="n">
         <f aca="false">C12/입력!C16</f>
         <v>684.782608695652</v>
       </c>
-      <c r="D16" s="55" t="n">
+      <c r="D16" s="57" t="n">
         <f aca="false">D12/입력!D16</f>
         <v>684.782608695652</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="55" t="n">
+      <c r="C17" s="57" t="n">
         <f aca="false">C16*입력!C15</f>
         <v>684.782608695652</v>
       </c>
-      <c r="D17" s="55" t="n">
+      <c r="D17" s="57" t="n">
         <f aca="false">D16*입력!D15</f>
-        <v>684.782608695652</v>
+        <v>595.760869565217</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="56" t="n">
+      <c r="C18" s="58" t="n">
         <f aca="false">ROUNDUP(입력!C6/C17,0)</f>
         <v>4</v>
       </c>
-      <c r="D18" s="56" t="n">
+      <c r="D18" s="58" t="n">
         <f aca="false">ROUNDUP(입력!D6/D17,0)</f>
-        <v>4</v>
-      </c>
-      <c r="F18" s="57" t="s">
-        <v>234</v>
+        <v>5</v>
+      </c>
+      <c r="F18" s="59" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="53" t="n">
+      <c r="C19" s="55" t="n">
         <f aca="false">ROUNDUP(입력!C6/C16,0)</f>
         <v>4</v>
       </c>
-      <c r="D19" s="53" t="n">
+      <c r="D19" s="55" t="n">
         <f aca="false">ROUNDUP(입력!D6/D16,0)</f>
         <v>4</v>
       </c>
-      <c r="F19" s="57" t="s">
-        <v>236</v>
+      <c r="F19" s="59" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="55" t="n">
+      <c r="C20" s="57" t="n">
         <f aca="false">C17*C18</f>
         <v>2739.13043478261</v>
       </c>
-      <c r="D20" s="55" t="n">
+      <c r="D20" s="57" t="n">
         <f aca="false">D17*D18</f>
-        <v>2739.13043478261</v>
-      </c>
-      <c r="F20" s="57"/>
+        <v>2978.80434782609</v>
+      </c>
+      <c r="F20" s="59"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>63</v>
@@ -21693,66 +21666,66 @@
       </c>
       <c r="D21" s="18" t="n">
         <f aca="false">입력!D6/D20</f>
-        <v>0.912698412698413</v>
-      </c>
-      <c r="F21" s="57"/>
+        <v>0.839262908228425</v>
+      </c>
+      <c r="F21" s="59"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="55" t="n">
+      <c r="C22" s="57" t="n">
         <f aca="false">C20-입력!C6</f>
         <v>239.130434782609</v>
       </c>
-      <c r="D22" s="55" t="n">
+      <c r="D22" s="57" t="n">
         <f aca="false">D20-입력!D6</f>
-        <v>239.130434782609</v>
-      </c>
-      <c r="F22" s="57"/>
+        <v>478.804347826087</v>
+      </c>
+      <c r="F22" s="59"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
         <v>91</v>
       </c>
       <c r="B23" s="8"/>
-      <c r="C23" s="58" t="str">
+      <c r="C23" s="60" t="str">
         <f aca="false">IF(C20&gt;=입력!C6,"충족","부족")</f>
         <v>충족</v>
       </c>
-      <c r="D23" s="58" t="str">
+      <c r="D23" s="60" t="str">
         <f aca="false">IF(D20&gt;=입력!D6,"충족","부족")</f>
         <v>충족</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="55" t="n">
+      <c r="C24" s="57" t="n">
         <f aca="false">C19*C17-입력!C6</f>
         <v>239.130434782609</v>
       </c>
-      <c r="D24" s="55" t="n">
+      <c r="D24" s="57" t="n">
         <f aca="false">D19*D17-입력!D6</f>
-        <v>239.130434782609</v>
-      </c>
-      <c r="F24" s="57" t="s">
-        <v>242</v>
+        <v>-116.956521739131</v>
+      </c>
+      <c r="F24" s="59" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -21762,40 +21735,40 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="53" t="n">
+      <c r="C26" s="55" t="n">
         <f aca="false">입력!C17*C18</f>
         <v>4</v>
       </c>
-      <c r="D26" s="53" t="n">
+      <c r="D26" s="55" t="n">
         <f aca="false">입력!D17*D18</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="53" t="n">
+      <c r="C27" s="55" t="n">
         <f aca="false">입력!C18*입력!C19</f>
         <v>4</v>
       </c>
-      <c r="D27" s="53" t="n">
+      <c r="D27" s="55" t="n">
         <f aca="false">입력!D18*입력!D19</f>
         <v>4</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21805,15 +21778,15 @@
       <c r="B28" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="53" t="n">
+      <c r="C28" s="55" t="n">
         <f aca="false">C26+C27</f>
         <v>8</v>
       </c>
-      <c r="D28" s="53" t="n">
+      <c r="D28" s="55" t="n">
         <f aca="false">D26+D27</f>
-        <v>8</v>
-      </c>
-      <c r="F28" s="57"/>
+        <v>9</v>
+      </c>
+      <c r="F28" s="59"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
@@ -21831,12 +21804,12 @@
         <v>55000</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>27</v>
@@ -21847,15 +21820,15 @@
       </c>
       <c r="D30" s="30" t="n">
         <f aca="false">D28*(입력!D40+입력!D41)*(1+입력!D42)</f>
-        <v>25600000</v>
+        <v>34128000</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>27</v>
@@ -21866,13 +21839,13 @@
       </c>
       <c r="D31" s="21" t="n">
         <f aca="false">D26*(입력!D40+입력!D41)*(1+입력!D42)/D29</f>
-        <v>232.727272727273</v>
-      </c>
-      <c r="F31" s="57"/>
+        <v>344.727272727273</v>
+      </c>
+      <c r="F31" s="59"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>27</v>
@@ -21883,9 +21856,9 @@
       </c>
       <c r="D32" s="21" t="n">
         <f aca="false">D27*(입력!D40+입력!D41)*(1+입력!D42)/D29</f>
-        <v>232.727272727273</v>
-      </c>
-      <c r="F32" s="57"/>
+        <v>275.781818181818</v>
+      </c>
+      <c r="F32" s="59"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true"/>
@@ -21931,7 +21904,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -21943,7 +21916,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="38" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -21955,173 +21928,173 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="61" t="str">
+        <v>264</v>
+      </c>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="63" t="str">
         <f aca="false">IF(B5="","",IF(C5&gt;0,B5/C5,""))</f>
         <v/>
       </c>
-      <c r="E5" s="62" t="str">
+      <c r="E5" s="64" t="str">
         <f aca="false">IF(B5="","",ROUNDUP(B5/CT계산!$C$14,0))</f>
         <v/>
       </c>
-      <c r="F5" s="62" t="str">
+      <c r="F5" s="64" t="str">
         <f aca="false">IF(B5="","",ROUNDUP(B5/CT계산!$D$14,0))</f>
         <v/>
       </c>
-      <c r="G5" s="63" t="str">
+      <c r="G5" s="65" t="str">
         <f aca="false">IF(OR(B5="",C5=""),"미측정",IF(D5&lt;=CT계산!$C$14,"충족","병목"))</f>
         <v>미측정</v>
       </c>
-      <c r="H5" s="63" t="str">
+      <c r="H5" s="65" t="str">
         <f aca="false">IF(OR(B5="",C5=""),"미측정",IF(D5&lt;=CT계산!$D$14,"충족","병목"))</f>
         <v>미측정</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="61" t="str">
+        <v>265</v>
+      </c>
+      <c r="B6" s="61"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="63" t="str">
         <f aca="false">IF(B6="","",IF(C6&gt;0,B6/C6,""))</f>
         <v/>
       </c>
-      <c r="E6" s="62" t="str">
+      <c r="E6" s="64" t="str">
         <f aca="false">IF(B6="","",ROUNDUP(B6/CT계산!$C$14,0))</f>
         <v/>
       </c>
-      <c r="F6" s="62" t="str">
+      <c r="F6" s="64" t="str">
         <f aca="false">IF(B6="","",ROUNDUP(B6/CT계산!$D$14,0))</f>
         <v/>
       </c>
-      <c r="G6" s="63" t="str">
+      <c r="G6" s="65" t="str">
         <f aca="false">IF(OR(B6="",C6=""),"미측정",IF(D6&lt;=CT계산!$C$14,"충족","병목"))</f>
         <v>미측정</v>
       </c>
-      <c r="H6" s="63" t="str">
+      <c r="H6" s="65" t="str">
         <f aca="false">IF(OR(B6="",C6=""),"미측정",IF(D6&lt;=CT계산!$D$14,"충족","병목"))</f>
         <v>미측정</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="61" t="str">
+        <v>266</v>
+      </c>
+      <c r="B7" s="61"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="63" t="str">
         <f aca="false">IF(B7="","",IF(C7&gt;0,B7/C7,""))</f>
         <v/>
       </c>
-      <c r="E7" s="62" t="str">
+      <c r="E7" s="64" t="str">
         <f aca="false">IF(B7="","",ROUNDUP(B7/CT계산!$C$14,0))</f>
         <v/>
       </c>
-      <c r="F7" s="62" t="str">
+      <c r="F7" s="64" t="str">
         <f aca="false">IF(B7="","",ROUNDUP(B7/CT계산!$D$14,0))</f>
         <v/>
       </c>
-      <c r="G7" s="63" t="str">
+      <c r="G7" s="65" t="str">
         <f aca="false">IF(OR(B7="",C7=""),"미측정",IF(D7&lt;=CT계산!$C$14,"충족","병목"))</f>
         <v>미측정</v>
       </c>
-      <c r="H7" s="63" t="str">
+      <c r="H7" s="65" t="str">
         <f aca="false">IF(OR(B7="",C7=""),"미측정",IF(D7&lt;=CT계산!$D$14,"충족","병목"))</f>
         <v>미측정</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="61" t="str">
+        <v>267</v>
+      </c>
+      <c r="B8" s="61"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="63" t="str">
         <f aca="false">IF(B8="","",IF(C8&gt;0,B8/C8,""))</f>
         <v/>
       </c>
-      <c r="E8" s="62" t="str">
+      <c r="E8" s="64" t="str">
         <f aca="false">IF(B8="","",ROUNDUP(B8/CT계산!$C$14,0))</f>
         <v/>
       </c>
-      <c r="F8" s="62" t="str">
+      <c r="F8" s="64" t="str">
         <f aca="false">IF(B8="","",ROUNDUP(B8/CT계산!$D$14,0))</f>
         <v/>
       </c>
-      <c r="G8" s="63" t="str">
+      <c r="G8" s="65" t="str">
         <f aca="false">IF(OR(B8="",C8=""),"미측정",IF(D8&lt;=CT계산!$C$14,"충족","병목"))</f>
         <v>미측정</v>
       </c>
-      <c r="H8" s="63" t="str">
+      <c r="H8" s="65" t="str">
         <f aca="false">IF(OR(B8="",C8=""),"미측정",IF(D8&lt;=CT계산!$D$14,"충족","병목"))</f>
         <v>미측정</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="61" t="str">
+        <v>268</v>
+      </c>
+      <c r="B9" s="61"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="63" t="str">
         <f aca="false">IF(B9="","",IF(C9&gt;0,B9/C9,""))</f>
         <v/>
       </c>
-      <c r="E9" s="62" t="str">
+      <c r="E9" s="64" t="str">
         <f aca="false">IF(B9="","",ROUNDUP(B9/CT계산!$C$14,0))</f>
         <v/>
       </c>
-      <c r="F9" s="62" t="str">
+      <c r="F9" s="64" t="str">
         <f aca="false">IF(B9="","",ROUNDUP(B9/CT계산!$D$14,0))</f>
         <v/>
       </c>
-      <c r="G9" s="63" t="str">
+      <c r="G9" s="65" t="str">
         <f aca="false">IF(OR(B9="",C9=""),"미측정",IF(D9&lt;=CT계산!$C$14,"충족","병목"))</f>
         <v>미측정</v>
       </c>
-      <c r="H9" s="63" t="str">
+      <c r="H9" s="65" t="str">
         <f aca="false">IF(OR(B9="",C9=""),"미측정",IF(D9&lt;=CT계산!$D$14,"충족","병목"))</f>
         <v>미측정</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="64" t="s">
-        <v>268</v>
+      <c r="A11" s="66" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="65" t="s">
-        <v>269</v>
+      <c r="A12" s="67" t="s">
+        <v>270</v>
       </c>
       <c r="E12" s="0" t="str">
         <f aca="false">IF(COUNT(B5:B9)=0,"미측정",SUM(E5:E9))</f>
@@ -22129,8 +22102,8 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="65" t="s">
-        <v>270</v>
+      <c r="A13" s="67" t="s">
+        <v>271</v>
       </c>
       <c r="F13" s="0" t="str">
         <f aca="false">IF(COUNT(B5:B9)=0,"미측정",SUM(F5:F9))</f>
@@ -22138,21 +22111,21 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="65" t="s">
-        <v>271</v>
-      </c>
-      <c r="E14" s="66" t="n">
+      <c r="A14" s="67" t="s">
+        <v>272</v>
+      </c>
+      <c r="E14" s="68" t="n">
         <f aca="false">CT계산!C27</f>
         <v>4</v>
       </c>
-      <c r="F14" s="66" t="n">
+      <c r="F14" s="68" t="n">
         <f aca="false">CT계산!D27</f>
         <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="64" t="s">
-        <v>272</v>
+      <c r="A15" s="66" t="s">
+        <v>273</v>
       </c>
       <c r="E15" s="0" t="str">
         <f aca="false">IF(ISNUMBER(E12),IF(E14&gt;=E12,"충분","부족 — 조 수/인원 증가 검토"),"미측정")</f>
@@ -22165,7 +22138,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -22216,7 +22189,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22228,7 +22201,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="38" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -22240,7 +22213,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -22252,176 +22225,176 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="67" t="n">
+      <c r="A6" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="B6" s="68" t="n">
+      <c r="B6" s="70" t="n">
         <f aca="false">입력!$C$6*$A6</f>
         <v>45000</v>
       </c>
-      <c r="C6" s="69" t="n">
+      <c r="C6" s="71" t="n">
         <f aca="false">((개당원가분석!$C$34-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A6))/(1-입력!$C$49))*(1+입력!$C$51)</f>
         <v>6547.49940356358</v>
       </c>
-      <c r="D6" s="70" t="n">
+      <c r="D6" s="72" t="n">
         <f aca="false">C6-개당원가분석!$C$37</f>
         <v>114.812121212121</v>
       </c>
-      <c r="E6" s="68" t="n">
+      <c r="E6" s="70" t="n">
         <f aca="false">입력!$D$6*$A6</f>
         <v>45000</v>
       </c>
-      <c r="F6" s="69" t="n">
+      <c r="F6" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A6))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6547.49940356358</v>
-      </c>
-      <c r="G6" s="70" t="n">
+        <v>6631.31673689691</v>
+      </c>
+      <c r="G6" s="72" t="n">
         <f aca="false">F6-개당원가분석!$D$37</f>
-        <v>114.812121212121</v>
+        <v>153.05890909091</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="67" t="n">
+      <c r="A7" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="B7" s="68" t="n">
+      <c r="B7" s="70" t="n">
         <f aca="false">입력!$C$6*$A7</f>
         <v>50000</v>
       </c>
-      <c r="C7" s="69" t="n">
+      <c r="C7" s="71" t="n">
         <f aca="false">((개당원가분석!$C$34-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A7))/(1-입력!$C$49))*(1+입력!$C$51)</f>
         <v>6484.35273689691</v>
       </c>
-      <c r="D7" s="70" t="n">
+      <c r="D7" s="72" t="n">
         <f aca="false">C7-개당원가분석!$C$37</f>
         <v>51.6654545454558</v>
       </c>
-      <c r="E7" s="68" t="n">
+      <c r="E7" s="70" t="n">
         <f aca="false">입력!$D$6*$A7</f>
         <v>50000</v>
       </c>
-      <c r="F7" s="69" t="n">
+      <c r="F7" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A7))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6484.35273689691</v>
-      </c>
-      <c r="G7" s="70" t="n">
+        <v>6547.13433689691</v>
+      </c>
+      <c r="G7" s="72" t="n">
         <f aca="false">F7-개당원가분석!$D$37</f>
-        <v>51.6654545454558</v>
+        <v>68.8765090909101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71" t="n">
+      <c r="A8" s="73" t="n">
         <v>22</v>
       </c>
-      <c r="B8" s="68" t="n">
+      <c r="B8" s="70" t="n">
         <f aca="false">입력!$C$6*$A8</f>
         <v>55000</v>
       </c>
-      <c r="C8" s="69" t="n">
+      <c r="C8" s="71" t="n">
         <f aca="false">((개당원가분석!$C$34-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A8))/(1-입력!$C$49))*(1+입력!$C$51)</f>
         <v>6432.68728235145</v>
       </c>
-      <c r="D8" s="70" t="n">
+      <c r="D8" s="72" t="n">
         <f aca="false">C8-개당원가분석!$C$37</f>
         <v>0</v>
       </c>
-      <c r="E8" s="68" t="n">
+      <c r="E8" s="70" t="n">
         <f aca="false">입력!$D$6*$A8</f>
         <v>55000</v>
       </c>
-      <c r="F8" s="69" t="n">
+      <c r="F8" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A8))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6432.68728235145</v>
-      </c>
-      <c r="G8" s="70" t="n">
+        <v>6478.257827806</v>
+      </c>
+      <c r="G8" s="72" t="n">
         <f aca="false">F8-개당원가분석!$D$37</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="67" t="n">
+      <c r="A9" s="69" t="n">
         <v>24</v>
       </c>
-      <c r="B9" s="68" t="n">
+      <c r="B9" s="70" t="n">
         <f aca="false">입력!$C$6*$A9</f>
         <v>60000</v>
       </c>
-      <c r="C9" s="69" t="n">
+      <c r="C9" s="71" t="n">
         <f aca="false">((개당원가분석!$C$34-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A9))/(1-입력!$C$49))*(1+입력!$C$51)</f>
         <v>6389.63273689691</v>
       </c>
-      <c r="D9" s="70" t="n">
+      <c r="D9" s="72" t="n">
         <f aca="false">C9-개당원가분석!$C$37</f>
         <v>-43.0545454545445</v>
       </c>
-      <c r="E9" s="68" t="n">
+      <c r="E9" s="70" t="n">
         <f aca="false">입력!$D$6*$A9</f>
         <v>60000</v>
       </c>
-      <c r="F9" s="69" t="n">
+      <c r="F9" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A9))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6389.63273689691</v>
-      </c>
-      <c r="G9" s="70" t="n">
+        <v>6420.86073689691</v>
+      </c>
+      <c r="G9" s="72" t="n">
         <f aca="false">F9-개당원가분석!$D$37</f>
-        <v>-43.0545454545445</v>
+        <v>-57.3970909090895</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="67" t="n">
+      <c r="A10" s="69" t="n">
         <v>26</v>
       </c>
-      <c r="B10" s="68" t="n">
+      <c r="B10" s="70" t="n">
         <f aca="false">입력!$C$6*$A10</f>
         <v>65000</v>
       </c>
-      <c r="C10" s="69" t="n">
+      <c r="C10" s="71" t="n">
         <f aca="false">((개당원가분석!$C$34-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A10))/(1-입력!$C$49))*(1+입력!$C$51)</f>
         <v>6353.20196766614</v>
       </c>
-      <c r="D10" s="70" t="n">
+      <c r="D10" s="72" t="n">
         <f aca="false">C10-개당원가분석!$C$37</f>
         <v>-79.4853146853138</v>
       </c>
-      <c r="E10" s="68" t="n">
+      <c r="E10" s="70" t="n">
         <f aca="false">입력!$D$6*$A10</f>
         <v>65000</v>
       </c>
-      <c r="F10" s="69" t="n">
+      <c r="F10" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A10))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6353.20196766614</v>
-      </c>
-      <c r="G10" s="70" t="n">
+        <v>6372.29396766614</v>
+      </c>
+      <c r="G10" s="72" t="n">
         <f aca="false">F10-개당원가분석!$D$37</f>
-        <v>-79.4853146853138</v>
+        <v>-105.963860139859</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -22433,198 +22406,198 @@
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="72" t="n">
+      <c r="A15" s="74" t="n">
         <v>0.8</v>
       </c>
-      <c r="B15" s="73" t="n">
+      <c r="B15" s="75" t="n">
         <f aca="false">CT계산!$D$19*CT계산!$D$12/입력!$D$16*$A15</f>
         <v>2191.30434782609</v>
       </c>
-      <c r="C15" s="74" t="n">
+      <c r="C15" s="76" t="n">
         <f aca="false">B15-입력!$D$6</f>
         <v>-308.695652173913</v>
       </c>
-      <c r="D15" s="75" t="n">
+      <c r="D15" s="77" t="n">
         <f aca="false">ROUNDUP(입력!$D$6/(CT계산!$D$12/입력!$D$16*$A15),0)</f>
         <v>5</v>
       </c>
-      <c r="E15" s="75" t="n">
+      <c r="E15" s="77" t="n">
         <f aca="false">D15*입력!$D$17+CT계산!$D$27</f>
         <v>9</v>
       </c>
-      <c r="F15" s="69" t="n">
+      <c r="F15" s="71" t="n">
         <f aca="false">E15*(입력!$D$40+입력!$D$41)*(1+입력!$D$42)/CT계산!$D$29</f>
-        <v>523.636363636364</v>
-      </c>
-      <c r="G15" s="69" t="n">
+        <v>620.509090909091</v>
+      </c>
+      <c r="G15" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F15)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6497.26910053327</v>
-      </c>
-      <c r="H15" s="76" t="str">
+        <v>6478.257827806</v>
+      </c>
+      <c r="H15" s="78" t="str">
         <f aca="false">IF(C15&gt;=0,"충족","부족")</f>
         <v>부족</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="72" t="n">
+      <c r="A16" s="74" t="n">
         <v>0.85</v>
       </c>
-      <c r="B16" s="73" t="n">
+      <c r="B16" s="75" t="n">
         <f aca="false">CT계산!$D$19*CT계산!$D$12/입력!$D$16*$A16</f>
         <v>2328.26086956522</v>
       </c>
-      <c r="C16" s="74" t="n">
+      <c r="C16" s="76" t="n">
         <f aca="false">B16-입력!$D$6</f>
         <v>-171.739130434783</v>
       </c>
-      <c r="D16" s="75" t="n">
+      <c r="D16" s="77" t="n">
         <f aca="false">ROUNDUP(입력!$D$6/(CT계산!$D$12/입력!$D$16*$A16),0)</f>
         <v>5</v>
       </c>
-      <c r="E16" s="75" t="n">
+      <c r="E16" s="77" t="n">
         <f aca="false">D16*입력!$D$17+CT계산!$D$27</f>
         <v>9</v>
       </c>
-      <c r="F16" s="69" t="n">
+      <c r="F16" s="71" t="n">
         <f aca="false">E16*(입력!$D$40+입력!$D$41)*(1+입력!$D$42)/CT계산!$D$29</f>
-        <v>523.636363636364</v>
-      </c>
-      <c r="G16" s="69" t="n">
+        <v>620.509090909091</v>
+      </c>
+      <c r="G16" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F16)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6497.26910053327</v>
-      </c>
-      <c r="H16" s="76" t="str">
+        <v>6478.257827806</v>
+      </c>
+      <c r="H16" s="78" t="str">
         <f aca="false">IF(C16&gt;=0,"충족","부족")</f>
         <v>부족</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="72" t="n">
+      <c r="A17" s="74" t="n">
         <v>0.9</v>
       </c>
-      <c r="B17" s="73" t="n">
+      <c r="B17" s="75" t="n">
         <f aca="false">CT계산!$D$19*CT계산!$D$12/입력!$D$16*$A17</f>
         <v>2465.21739130435</v>
       </c>
-      <c r="C17" s="74" t="n">
+      <c r="C17" s="76" t="n">
         <f aca="false">B17-입력!$D$6</f>
         <v>-34.7826086956525</v>
       </c>
-      <c r="D17" s="75" t="n">
+      <c r="D17" s="77" t="n">
         <f aca="false">ROUNDUP(입력!$D$6/(CT계산!$D$12/입력!$D$16*$A17),0)</f>
         <v>5</v>
       </c>
-      <c r="E17" s="75" t="n">
+      <c r="E17" s="77" t="n">
         <f aca="false">D17*입력!$D$17+CT계산!$D$27</f>
         <v>9</v>
       </c>
-      <c r="F17" s="69" t="n">
+      <c r="F17" s="71" t="n">
         <f aca="false">E17*(입력!$D$40+입력!$D$41)*(1+입력!$D$42)/CT계산!$D$29</f>
-        <v>523.636363636364</v>
-      </c>
-      <c r="G17" s="69" t="n">
+        <v>620.509090909091</v>
+      </c>
+      <c r="G17" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F17)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6497.26910053327</v>
-      </c>
-      <c r="H17" s="76" t="str">
+        <v>6478.257827806</v>
+      </c>
+      <c r="H17" s="78" t="str">
         <f aca="false">IF(C17&gt;=0,"충족","부족")</f>
         <v>부족</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="72" t="n">
+      <c r="A18" s="74" t="n">
         <v>0.95</v>
       </c>
-      <c r="B18" s="73" t="n">
+      <c r="B18" s="75" t="n">
         <f aca="false">CT계산!$D$19*CT계산!$D$12/입력!$D$16*$A18</f>
         <v>2602.17391304348</v>
       </c>
-      <c r="C18" s="74" t="n">
+      <c r="C18" s="76" t="n">
         <f aca="false">B18-입력!$D$6</f>
         <v>102.173913043478</v>
       </c>
-      <c r="D18" s="75" t="n">
+      <c r="D18" s="77" t="n">
         <f aca="false">ROUNDUP(입력!$D$6/(CT계산!$D$12/입력!$D$16*$A18),0)</f>
         <v>4</v>
       </c>
-      <c r="E18" s="75" t="n">
+      <c r="E18" s="77" t="n">
         <f aca="false">D18*입력!$D$17+CT계산!$D$27</f>
         <v>8</v>
       </c>
-      <c r="F18" s="69" t="n">
+      <c r="F18" s="71" t="n">
         <f aca="false">E18*(입력!$D$40+입력!$D$41)*(1+입력!$D$42)/CT계산!$D$29</f>
-        <v>465.454545454545</v>
-      </c>
-      <c r="G18" s="69" t="n">
+        <v>551.563636363636</v>
+      </c>
+      <c r="G18" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F18)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6432.68728235145</v>
-      </c>
-      <c r="H18" s="76" t="str">
+        <v>6401.72837326055</v>
+      </c>
+      <c r="H18" s="78" t="str">
         <f aca="false">IF(C18&gt;=0,"충족","부족")</f>
         <v>충족</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="72" t="n">
+      <c r="A19" s="74" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="73" t="n">
+      <c r="B19" s="75" t="n">
         <f aca="false">CT계산!$D$19*CT계산!$D$12/입력!$D$16*$A19</f>
         <v>2739.13043478261</v>
       </c>
-      <c r="C19" s="74" t="n">
+      <c r="C19" s="76" t="n">
         <f aca="false">B19-입력!$D$6</f>
         <v>239.130434782609</v>
       </c>
-      <c r="D19" s="75" t="n">
+      <c r="D19" s="77" t="n">
         <f aca="false">ROUNDUP(입력!$D$6/(CT계산!$D$12/입력!$D$16*$A19),0)</f>
         <v>4</v>
       </c>
-      <c r="E19" s="75" t="n">
+      <c r="E19" s="77" t="n">
         <f aca="false">D19*입력!$D$17+CT계산!$D$27</f>
         <v>8</v>
       </c>
-      <c r="F19" s="69" t="n">
+      <c r="F19" s="71" t="n">
         <f aca="false">E19*(입력!$D$40+입력!$D$41)*(1+입력!$D$42)/CT계산!$D$29</f>
-        <v>465.454545454545</v>
-      </c>
-      <c r="G19" s="69" t="n">
+        <v>551.563636363636</v>
+      </c>
+      <c r="G19" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F19)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6432.68728235145</v>
-      </c>
-      <c r="H19" s="76" t="str">
+        <v>6401.72837326055</v>
+      </c>
+      <c r="H19" s="78" t="str">
         <f aca="false">IF(C19&gt;=0,"충족","부족")</f>
         <v>충족</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -22636,16 +22609,16 @@
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -22653,71 +22626,71 @@
       <c r="H22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="71" t="n">
+      <c r="A23" s="73" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="69" t="n">
+      <c r="B23" s="71" t="n">
         <f aca="false">입력!$D$35/$A23</f>
         <v>120</v>
       </c>
-      <c r="C23" s="69" t="n">
+      <c r="C23" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-개당원가분석!$D$17+B23)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6432.68728235145</v>
-      </c>
-      <c r="D23" s="70" t="n">
+        <v>6604.797827806</v>
+      </c>
+      <c r="D23" s="72" t="n">
         <f aca="false">C23-개당원가분석!$D$37</f>
-        <v>0</v>
+        <v>126.540000000001</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="71" t="n">
+      <c r="A24" s="73" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="69" t="n">
+      <c r="B24" s="71" t="n">
         <f aca="false">입력!$D$35/$A24</f>
         <v>24</v>
       </c>
-      <c r="C24" s="69" t="n">
+      <c r="C24" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-개당원가분석!$D$17+B24)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6326.12728235145</v>
-      </c>
-      <c r="D24" s="70" t="n">
+        <v>6498.237827806</v>
+      </c>
+      <c r="D24" s="72" t="n">
         <f aca="false">C24-개당원가분석!$D$37</f>
-        <v>-106.559999999999</v>
+        <v>19.9800000000005</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71" t="n">
+      <c r="A25" s="73" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="69" t="n">
+      <c r="B25" s="71" t="n">
         <f aca="false">입력!$D$35/$A25</f>
         <v>12</v>
       </c>
-      <c r="C25" s="69" t="n">
+      <c r="C25" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-개당원가분석!$D$17+B25)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6312.80728235145</v>
-      </c>
-      <c r="D25" s="70" t="n">
+        <v>6484.917827806</v>
+      </c>
+      <c r="D25" s="72" t="n">
         <f aca="false">C25-개당원가분석!$D$37</f>
-        <v>-119.88</v>
+        <v>6.66000000000076</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="71" t="n">
+      <c r="A26" s="73" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="69" t="n">
+      <c r="B26" s="71" t="n">
         <f aca="false">입력!$D$35/$A26</f>
         <v>6</v>
       </c>
-      <c r="C26" s="69" t="n">
+      <c r="C26" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-개당원가분석!$D$17+B26)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6306.14728235145</v>
-      </c>
-      <c r="D26" s="70" t="n">
+        <v>6478.257827806</v>
+      </c>
+      <c r="D26" s="72" t="n">
         <f aca="false">C26-개당원가분석!$D$37</f>
-        <v>-126.54</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -22760,7 +22733,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22771,7 +22744,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="38" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -22782,462 +22755,462 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="F5" s="77" t="s">
         <v>311</v>
       </c>
+      <c r="F5" s="79" t="s">
+        <v>312</v>
+      </c>
       <c r="G5" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="F6" s="77" t="s">
-        <v>311</v>
+        <v>317</v>
+      </c>
+      <c r="F6" s="79" t="s">
+        <v>312</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="F7" s="77" t="s">
-        <v>311</v>
+        <v>322</v>
+      </c>
+      <c r="F7" s="79" t="s">
+        <v>312</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="F8" s="78" t="s">
         <v>327</v>
       </c>
+      <c r="F8" s="80" t="s">
+        <v>328</v>
+      </c>
       <c r="G8" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="F9" s="77" t="s">
-        <v>311</v>
+        <v>333</v>
+      </c>
+      <c r="F9" s="79" t="s">
+        <v>312</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="F10" s="77" t="s">
-        <v>311</v>
+        <v>338</v>
+      </c>
+      <c r="F10" s="79" t="s">
+        <v>312</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="F11" s="77" t="s">
-        <v>311</v>
+        <v>343</v>
+      </c>
+      <c r="F11" s="79" t="s">
+        <v>312</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="F12" s="77" t="s">
-        <v>311</v>
+        <v>348</v>
+      </c>
+      <c r="F12" s="79" t="s">
+        <v>312</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="F13" s="79" t="s">
         <v>353</v>
       </c>
+      <c r="F13" s="81" t="s">
+        <v>354</v>
+      </c>
       <c r="G13" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="F14" s="77" t="s">
-        <v>311</v>
+        <v>360</v>
+      </c>
+      <c r="F14" s="79" t="s">
+        <v>312</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="F15" s="77" t="s">
-        <v>311</v>
+        <v>365</v>
+      </c>
+      <c r="F15" s="79" t="s">
+        <v>312</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="F16" s="78" t="s">
         <v>370</v>
       </c>
+      <c r="F16" s="80" t="s">
+        <v>371</v>
+      </c>
       <c r="G16" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="F17" s="78" t="s">
-        <v>370</v>
+        <v>376</v>
+      </c>
+      <c r="F17" s="80" t="s">
+        <v>371</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F18" s="78" t="s">
-        <v>370</v>
+        <v>381</v>
+      </c>
+      <c r="F18" s="80" t="s">
+        <v>371</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="F19" s="78" t="s">
-        <v>370</v>
+        <v>386</v>
+      </c>
+      <c r="F19" s="80" t="s">
+        <v>371</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="F20" s="77" t="s">
-        <v>311</v>
+        <v>391</v>
+      </c>
+      <c r="F20" s="79" t="s">
+        <v>312</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="F21" s="77" t="s">
-        <v>311</v>
+        <v>396</v>
+      </c>
+      <c r="F21" s="79" t="s">
+        <v>312</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="F22" s="78" t="s">
-        <v>370</v>
+        <v>401</v>
+      </c>
+      <c r="F22" s="80" t="s">
+        <v>371</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="F23" s="79" t="s">
         <v>407</v>
       </c>
+      <c r="F23" s="81" t="s">
+        <v>408</v>
+      </c>
       <c r="G23" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -23277,7 +23250,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -23290,7 +23263,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="38" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -23303,482 +23276,482 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="E5" s="80"/>
+        <v>422</v>
+      </c>
+      <c r="E5" s="82"/>
       <c r="F5" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="H5" s="81" t="s">
+        <v>424</v>
+      </c>
+      <c r="H5" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I5" s="82"/>
+      <c r="I5" s="84"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="E6" s="82"/>
+      <c r="F6" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="E6" s="80"/>
-      <c r="F6" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="H6" s="81" t="s">
+      <c r="H6" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I6" s="82"/>
+      <c r="I6" s="84"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="E7" s="80"/>
+        <v>431</v>
+      </c>
+      <c r="E7" s="82"/>
       <c r="F7" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="H7" s="81" t="s">
+        <v>433</v>
+      </c>
+      <c r="H7" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I7" s="82"/>
+      <c r="I7" s="84"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="E8" s="80"/>
+        <v>436</v>
+      </c>
+      <c r="E8" s="82"/>
       <c r="F8" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="H8" s="81" t="s">
+        <v>438</v>
+      </c>
+      <c r="H8" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I8" s="82"/>
+      <c r="I8" s="84"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="E9" s="80"/>
+        <v>441</v>
+      </c>
+      <c r="E9" s="82"/>
       <c r="F9" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="H9" s="81" t="s">
+        <v>443</v>
+      </c>
+      <c r="H9" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I9" s="82"/>
+      <c r="I9" s="84"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="E10" s="80"/>
+        <v>446</v>
+      </c>
+      <c r="E10" s="82"/>
       <c r="F10" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="H10" s="81" t="s">
+        <v>433</v>
+      </c>
+      <c r="H10" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I10" s="82"/>
+      <c r="I10" s="84"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="E11" s="80"/>
+        <v>450</v>
+      </c>
+      <c r="E11" s="82"/>
       <c r="F11" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="H11" s="81" t="s">
+        <v>452</v>
+      </c>
+      <c r="H11" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I11" s="82"/>
+      <c r="I11" s="84"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="E12" s="80"/>
+        <v>455</v>
+      </c>
+      <c r="E12" s="82"/>
       <c r="F12" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="H12" s="81" t="s">
+        <v>424</v>
+      </c>
+      <c r="H12" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="82"/>
+      <c r="I12" s="84"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="E13" s="80"/>
+        <v>459</v>
+      </c>
+      <c r="E13" s="82"/>
       <c r="F13" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="H13" s="81" t="s">
+        <v>424</v>
+      </c>
+      <c r="H13" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I13" s="82"/>
+      <c r="I13" s="84"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="E14" s="80"/>
+        <v>463</v>
+      </c>
+      <c r="E14" s="82"/>
       <c r="F14" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="H14" s="81" t="s">
+        <v>465</v>
+      </c>
+      <c r="H14" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I14" s="82"/>
+      <c r="I14" s="84"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="E15" s="80"/>
+        <v>468</v>
+      </c>
+      <c r="E15" s="82"/>
       <c r="F15" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="H15" s="81" t="s">
+        <v>470</v>
+      </c>
+      <c r="H15" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I15" s="82"/>
+      <c r="I15" s="84"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="E16" s="80"/>
+        <v>473</v>
+      </c>
+      <c r="E16" s="82"/>
       <c r="F16" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="H16" s="81" t="s">
+        <v>475</v>
+      </c>
+      <c r="H16" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I16" s="82"/>
+      <c r="I16" s="84"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="E17" s="80"/>
+        <v>478</v>
+      </c>
+      <c r="E17" s="82"/>
       <c r="F17" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="H17" s="81" t="s">
+        <v>480</v>
+      </c>
+      <c r="H17" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I17" s="82"/>
+      <c r="I17" s="84"/>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="E18" s="80"/>
+        <v>483</v>
+      </c>
+      <c r="E18" s="82"/>
       <c r="F18" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="H18" s="81" t="s">
+        <v>485</v>
+      </c>
+      <c r="H18" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I18" s="82"/>
+      <c r="I18" s="84"/>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="E19" s="80"/>
+        <v>488</v>
+      </c>
+      <c r="E19" s="82"/>
       <c r="F19" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="H19" s="81" t="s">
+        <v>490</v>
+      </c>
+      <c r="H19" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I19" s="82"/>
+      <c r="I19" s="84"/>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="E20" s="80"/>
+        <v>493</v>
+      </c>
+      <c r="E20" s="82"/>
       <c r="F20" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="H20" s="81" t="s">
+        <v>495</v>
+      </c>
+      <c r="H20" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I20" s="82"/>
+      <c r="I20" s="84"/>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="E21" s="80"/>
+        <v>498</v>
+      </c>
+      <c r="E21" s="82"/>
       <c r="F21" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="H21" s="81" t="s">
+        <v>500</v>
+      </c>
+      <c r="H21" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I21" s="82"/>
+      <c r="I21" s="84"/>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="E22" s="80"/>
+        <v>503</v>
+      </c>
+      <c r="E22" s="82"/>
       <c r="F22" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="H22" s="81" t="s">
+        <v>505</v>
+      </c>
+      <c r="H22" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="I22" s="82"/>
+      <c r="I22" s="84"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true"/>
@@ -23818,7 +23791,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -23828,7 +23801,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -23838,51 +23811,51 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
+        <v>515</v>
+      </c>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
     </row>
     <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
+        <v>518</v>
+      </c>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true"/>

--- a/SHINHWA_QMS_WORKFLOW/12_OUTPUT/REPORTS/개당원가분석표_R2_20261028.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/12_OUTPUT/REPORTS/개당원가분석표_R2_20261028.xlsx
@@ -18565,7 +18565,7 @@
       </c>
       <c r="B6" s="10" t="str">
         <f aca="false">COUNTIF(입력!G6:G53,"확인완료")&amp;" / 44 항목 확인완료"</f>
-        <v>3 / 44 항목 확인완료</v>
+        <v>5 / 44 항목 확인완료</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -18674,15 +18674,15 @@
       </c>
       <c r="D13" s="17" t="n">
         <f aca="false">(D11+D12)*입력!D21*(1+입력!D27)</f>
-        <v>2910.75922242965</v>
+        <v>2998.08199910254</v>
       </c>
       <c r="E13" s="17" t="n">
         <f aca="false">D13-C13</f>
-        <v>0</v>
+        <v>87.3227766728896</v>
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">IF(C13=0,"-",D13/C13-1)</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>28</v>
@@ -18853,15 +18853,15 @@
       </c>
       <c r="D20" s="24" t="n">
         <f aca="false">D13+D19</f>
-        <v>5135.75922242965</v>
+        <v>5223.08199910254</v>
       </c>
       <c r="E20" s="24" t="n">
         <f aca="false">D20-C20</f>
-        <v>-114</v>
+        <v>-26.6772233271095</v>
       </c>
       <c r="F20" s="25" t="n">
         <f aca="false">IF(C20=0,"-",D20/C20-1)</f>
-        <v>-0.0217152816290953</v>
+        <v>-0.00508160892658294</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>37</v>
@@ -19183,15 +19183,15 @@
       </c>
       <c r="D34" s="24" t="n">
         <f aca="false">D20+D32</f>
-        <v>5836.26831333874</v>
+        <v>5923.59109001163</v>
       </c>
       <c r="E34" s="24" t="n">
         <f aca="false">D34-C34</f>
-        <v>41.0545454545445</v>
+        <v>128.377322127435</v>
       </c>
       <c r="F34" s="25" t="n">
         <f aca="false">IF(C34=0,"-",D34/C34-1)</f>
-        <v>0.007084215888991</v>
+        <v>0.022152301411015</v>
       </c>
       <c r="G34" s="27" t="s">
         <v>54</v>
@@ -19210,15 +19210,15 @@
       </c>
       <c r="D35" s="24" t="n">
         <f aca="false">D34/(1-입력!D49)</f>
-        <v>5836.26831333874</v>
+        <v>6044.4807040935</v>
       </c>
       <c r="E35" s="24" t="n">
         <f aca="false">D35-C35</f>
-        <v>41.0545454545445</v>
+        <v>249.266936209305</v>
       </c>
       <c r="F35" s="25" t="n">
         <f aca="false">IF(C35=0,"-",D35/C35-1)</f>
-        <v>0.007084215888991</v>
+        <v>0.0430125524602194</v>
       </c>
       <c r="G35" s="26" t="s">
         <v>56</v>
@@ -19237,15 +19237,15 @@
       </c>
       <c r="D36" s="17" t="n">
         <f aca="false">D35*입력!D51</f>
-        <v>641.989514467261</v>
+        <v>664.892877450285</v>
       </c>
       <c r="E36" s="17" t="n">
         <f aca="false">D36-C36</f>
-        <v>4.51599999999985</v>
+        <v>27.4193629830235</v>
       </c>
       <c r="F36" s="18" t="n">
         <f aca="false">IF(C36=0,"-",D36/C36-1)</f>
-        <v>0.007084215888991</v>
+        <v>0.0430125524602194</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>58</v>
@@ -19264,15 +19264,15 @@
       </c>
       <c r="D37" s="24" t="n">
         <f aca="false">D35+D36</f>
-        <v>6478.257827806</v>
+        <v>6709.37358154378</v>
       </c>
       <c r="E37" s="24" t="n">
         <f aca="false">D37-C37</f>
-        <v>45.5705454545441</v>
+        <v>276.686299192328</v>
       </c>
       <c r="F37" s="25" t="n">
         <f aca="false">IF(C37=0,"-",D37/C37-1)</f>
-        <v>0.007084215888991</v>
+        <v>0.0430125524602194</v>
       </c>
       <c r="G37" s="27"/>
     </row>
@@ -19289,15 +19289,15 @@
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">D37*입력!D53</f>
-        <v>647.8257827806</v>
+        <v>670.937358154378</v>
       </c>
       <c r="E38" s="17" t="n">
         <f aca="false">D38-C38</f>
-        <v>4.55705454545443</v>
+        <v>27.6686299192329</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">IF(C38=0,"-",D38/C38-1)</f>
-        <v>0.007084215888991</v>
+        <v>0.0430125524602196</v>
       </c>
       <c r="G38" s="8"/>
     </row>
@@ -19314,15 +19314,15 @@
       </c>
       <c r="D39" s="17" t="n">
         <f aca="false">D37+D38</f>
-        <v>7126.0836105866</v>
+        <v>7380.31093969816</v>
       </c>
       <c r="E39" s="17" t="n">
         <f aca="false">D39-C39</f>
-        <v>50.1275999999989</v>
+        <v>304.354929111561</v>
       </c>
       <c r="F39" s="18" t="n">
         <f aca="false">IF(C39=0,"-",D39/C39-1)</f>
-        <v>0.007084215888991</v>
+        <v>0.0430125524602194</v>
       </c>
       <c r="G39" s="8"/>
     </row>
@@ -19363,15 +19363,15 @@
       </c>
       <c r="D41" s="17" t="n">
         <f aca="false">D35/(1-입력!D52)</f>
-        <v>6557.60484644802</v>
+        <v>6791.55135291404</v>
       </c>
       <c r="E41" s="17" t="n">
         <f aca="false">D41-C41</f>
-        <v>46.1287027579147</v>
+        <v>280.075209223937</v>
       </c>
       <c r="F41" s="18" t="n">
         <f aca="false">IF(C41=0,"-",D41/C41-1)</f>
-        <v>0.007084215888991</v>
+        <v>0.0430125524602194</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>66</v>
@@ -19390,15 +19390,15 @@
       </c>
       <c r="D42" s="17" t="n">
         <f aca="false">D41-D37</f>
-        <v>79.3470186420209</v>
+        <v>82.1777713702595</v>
       </c>
       <c r="E42" s="17" t="n">
         <f aca="false">D42-C42</f>
-        <v>0.558157303370535</v>
+        <v>3.38891003160916</v>
       </c>
       <c r="F42" s="18" t="n">
         <f aca="false">IF(C42=0,"-",D42/C42-1)</f>
-        <v>0.00708421588898789</v>
+        <v>0.0430125524602132</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>68</v>
@@ -19428,11 +19428,11 @@
       </c>
       <c r="D44" s="18" t="n">
         <f aca="false">D20/D37</f>
-        <v>0.792768574351259</v>
+        <v>0.778475357739841</v>
       </c>
       <c r="E44" s="18" t="n">
         <f aca="false">D44-C44</f>
-        <v>-0.0233381306696335</v>
+        <v>-0.0376313472810513</v>
       </c>
       <c r="F44" s="29"/>
       <c r="G44" s="8"/>
@@ -19450,11 +19450,11 @@
       </c>
       <c r="D45" s="18" t="n">
         <f aca="false">D24/D37</f>
-        <v>0.0957833274627848</v>
+        <v>0.0924839082766227</v>
       </c>
       <c r="E45" s="18" t="n">
         <f aca="false">D45-C45</f>
-        <v>0.023425613645178</v>
+        <v>0.0201261944590159</v>
       </c>
       <c r="F45" s="29"/>
       <c r="G45" s="8"/>
@@ -19472,11 +19472,11 @@
       </c>
       <c r="D46" s="18" t="n">
         <f aca="false">D31/D37</f>
-        <v>0.0123489990868569</v>
+        <v>0.0119236168664188</v>
       </c>
       <c r="E46" s="18" t="n">
         <f aca="false">D46-C46</f>
-        <v>-8.74829755442459E-005</v>
+        <v>-0.000512865195982395</v>
       </c>
       <c r="F46" s="29"/>
       <c r="G46" s="8"/>
@@ -19494,11 +19494,11 @@
       </c>
       <c r="D47" s="18" t="n">
         <f aca="false">(D35-D34)/D37</f>
-        <v>0</v>
+        <v>0.018018018018018</v>
       </c>
       <c r="E47" s="18" t="n">
         <f aca="false">D47-C47</f>
-        <v>0</v>
+        <v>0.018018018018018</v>
       </c>
       <c r="F47" s="29"/>
       <c r="G47" s="8"/>
@@ -19549,15 +19549,15 @@
       </c>
       <c r="D50" s="30" t="n">
         <f aca="false">D37*입력!D6</f>
-        <v>16195644.569515</v>
+        <v>16773433.9538595</v>
       </c>
       <c r="E50" s="17" t="n">
         <f aca="false">D50-C50</f>
-        <v>113926.363636361</v>
+        <v>691715.747980822</v>
       </c>
       <c r="F50" s="18" t="n">
         <f aca="false">IF(C50=0,"-",D50/C50-1)</f>
-        <v>0.007084215888991</v>
+        <v>0.0430125524602196</v>
       </c>
       <c r="G50" s="8"/>
     </row>
@@ -19599,15 +19599,15 @@
       </c>
       <c r="D52" s="30" t="n">
         <f aca="false">D37*D51</f>
-        <v>356304180.52933</v>
+        <v>369015546.984908</v>
       </c>
       <c r="E52" s="17" t="n">
         <f aca="false">D52-C52</f>
-        <v>2506379.99999994</v>
+        <v>15217746.4555781</v>
       </c>
       <c r="F52" s="18" t="n">
         <f aca="false">IF(C52=0,"-",D52/C52-1)</f>
-        <v>0.007084215888991</v>
+        <v>0.0430125524602196</v>
       </c>
       <c r="G52" s="8"/>
     </row>
@@ -19624,15 +19624,15 @@
       </c>
       <c r="D53" s="30" t="n">
         <f aca="false">D36*D51</f>
-        <v>35309423.2956994</v>
+        <v>36569108.2597657</v>
       </c>
       <c r="E53" s="17" t="n">
         <f aca="false">D53-C53</f>
-        <v>248379.999999993</v>
+        <v>1508064.9640663</v>
       </c>
       <c r="F53" s="18" t="n">
         <f aca="false">IF(C53=0,"-",D53/C53-1)</f>
-        <v>0.007084215888991</v>
+        <v>0.0430125524602196</v>
       </c>
       <c r="G53" s="8"/>
     </row>
@@ -20538,17 +20538,17 @@
       <c r="C27" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="46" t="n">
-        <v>0</v>
+      <c r="D27" s="47" t="n">
+        <v>0.03</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="F27" s="41" t="s">
         <v>163</v>
       </c>
       <c r="G27" s="42" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21006,17 +21006,17 @@
       <c r="C49" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D49" s="46" t="n">
-        <v>0</v>
+      <c r="D49" s="47" t="n">
+        <v>0.02</v>
       </c>
       <c r="E49" s="40" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="F49" s="41" t="s">
         <v>197</v>
       </c>
       <c r="G49" s="42" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22269,11 +22269,11 @@
       </c>
       <c r="F6" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A6))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6631.31673689691</v>
+        <v>6865.55614184063</v>
       </c>
       <c r="G6" s="72" t="n">
         <f aca="false">F6-개당원가분석!$D$37</f>
-        <v>153.05890909091</v>
+        <v>156.182560296847</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22298,11 +22298,11 @@
       </c>
       <c r="F7" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A7))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6547.13433689691</v>
+        <v>6779.65573367736</v>
       </c>
       <c r="G7" s="72" t="n">
         <f aca="false">F7-개당원가분석!$D$37</f>
-        <v>68.8765090909101</v>
+        <v>70.2821521335809</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22327,7 +22327,7 @@
       </c>
       <c r="F8" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A8))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6478.257827806</v>
+        <v>6709.37358154378</v>
       </c>
       <c r="G8" s="72" t="n">
         <f aca="false">F8-개당원가분석!$D$37</f>
@@ -22356,11 +22356,11 @@
       </c>
       <c r="F9" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A9))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6420.86073689691</v>
+        <v>6650.80512143247</v>
       </c>
       <c r="G9" s="72" t="n">
         <f aca="false">F9-개당원가분석!$D$37</f>
-        <v>-57.3970909090895</v>
+        <v>-58.5684601113153</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22385,11 +22385,11 @@
       </c>
       <c r="F10" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A10))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6372.29396766614</v>
+        <v>6601.24719364597</v>
       </c>
       <c r="G10" s="72" t="n">
         <f aca="false">F10-개당원가분석!$D$37</f>
-        <v>-105.963860139859</v>
+        <v>-108.126387897815</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22456,7 +22456,7 @@
       </c>
       <c r="G15" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F15)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6478.257827806</v>
+        <v>6709.37358154378</v>
       </c>
       <c r="H15" s="78" t="str">
         <f aca="false">IF(C15&gt;=0,"충족","부족")</f>
@@ -22489,7 +22489,7 @@
       </c>
       <c r="G16" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F16)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6478.257827806</v>
+        <v>6709.37358154378</v>
       </c>
       <c r="H16" s="78" t="str">
         <f aca="false">IF(C16&gt;=0,"충족","부족")</f>
@@ -22522,7 +22522,7 @@
       </c>
       <c r="G17" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F17)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6478.257827806</v>
+        <v>6709.37358154378</v>
       </c>
       <c r="H17" s="78" t="str">
         <f aca="false">IF(C17&gt;=0,"충족","부족")</f>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="G18" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F18)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6401.72837326055</v>
+        <v>6631.28230139536</v>
       </c>
       <c r="H18" s="78" t="str">
         <f aca="false">IF(C18&gt;=0,"충족","부족")</f>
@@ -22588,7 +22588,7 @@
       </c>
       <c r="G19" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F19)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6401.72837326055</v>
+        <v>6631.28230139536</v>
       </c>
       <c r="H19" s="78" t="str">
         <f aca="false">IF(C19&gt;=0,"충족","부족")</f>
@@ -22635,11 +22635,11 @@
       </c>
       <c r="C23" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-개당원가분석!$D$17+B23)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6604.797827806</v>
+        <v>6838.49603052337</v>
       </c>
       <c r="D23" s="72" t="n">
         <f aca="false">C23-개당원가분석!$D$37</f>
-        <v>126.540000000001</v>
+        <v>129.122448979592</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22652,11 +22652,11 @@
       </c>
       <c r="C24" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-개당원가분석!$D$17+B24)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6498.237827806</v>
+        <v>6729.76133664582</v>
       </c>
       <c r="D24" s="72" t="n">
         <f aca="false">C24-개당원가분석!$D$37</f>
-        <v>19.9800000000005</v>
+        <v>20.3877551020414</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22669,11 +22669,11 @@
       </c>
       <c r="C25" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-개당원가분석!$D$17+B25)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6484.917827806</v>
+        <v>6716.16949991113</v>
       </c>
       <c r="D25" s="72" t="n">
         <f aca="false">C25-개당원가분석!$D$37</f>
-        <v>6.66000000000076</v>
+        <v>6.79591836734835</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="C26" s="71" t="n">
         <f aca="false">((개당원가분석!$D$34-개당원가분석!$D$17+B26)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6478.257827806</v>
+        <v>6709.37358154378</v>
       </c>
       <c r="D26" s="72" t="n">
         <f aca="false">C26-개당원가분석!$D$37</f>

--- a/SHINHWA_QMS_WORKFLOW/12_OUTPUT/REPORTS/개당원가분석표_R2_20261028.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/12_OUTPUT/REPORTS/개당원가분석표_R2_20261028.xlsx
@@ -1700,7 +1700,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제조원가 </t>
+      <t xml:space="preserve">재료비 </t>
     </r>
     <r>
       <rPr>
@@ -1720,6 +1720,63 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">불량률</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공정비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. OEE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 양품률을 포함하므로 공정비는 불량 보정 제외</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이중 계산 방지</t>
     </r>
     <r>
       <rPr>
@@ -6716,7 +6773,121 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">양품 기준 원가에 반영</t>
+      <t xml:space="preserve">폐기 재료비에 반영</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양품 기준 재료비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재료비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷(1-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불량률</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)). OEE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 양품률 포함값이므로 공정비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인원은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OEE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에서 이미 반영</t>
     </r>
     <r>
       <rPr>
@@ -12898,75 +13069,109 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양품 기준 직접원가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재료비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷(1-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불량률</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공정비 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(OEE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 양품률 포함 → 공정비는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OEE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 반영해 이중 계산 방지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">양품 기준 직접원가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제조원가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷(1-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불량률</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 반영</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -19205,20 +19410,20 @@
         <v>27</v>
       </c>
       <c r="C35" s="24" t="n">
-        <f aca="false">C34/(1-입력!C49)</f>
+        <f aca="false">C20/(1-입력!C49)+C32</f>
         <v>5795.21376788419</v>
       </c>
       <c r="D35" s="24" t="n">
-        <f aca="false">D34/(1-입력!D49)</f>
-        <v>6044.4807040935</v>
+        <f aca="false">D20/(1-입력!D49)+D32</f>
+        <v>6030.18460019739</v>
       </c>
       <c r="E35" s="24" t="n">
         <f aca="false">D35-C35</f>
-        <v>249.266936209305</v>
+        <v>234.970832313202</v>
       </c>
       <c r="F35" s="25" t="n">
         <f aca="false">IF(C35=0,"-",D35/C35-1)</f>
-        <v>0.0430125524602194</v>
+        <v>0.0405456712598522</v>
       </c>
       <c r="G35" s="26" t="s">
         <v>56</v>
@@ -19237,15 +19442,15 @@
       </c>
       <c r="D36" s="17" t="n">
         <f aca="false">D35*입력!D51</f>
-        <v>664.892877450285</v>
+        <v>663.320306021713</v>
       </c>
       <c r="E36" s="17" t="n">
         <f aca="false">D36-C36</f>
-        <v>27.4193629830235</v>
+        <v>25.8467915544522</v>
       </c>
       <c r="F36" s="18" t="n">
         <f aca="false">IF(C36=0,"-",D36/C36-1)</f>
-        <v>0.0430125524602194</v>
+        <v>0.0405456712598522</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>58</v>
@@ -19264,15 +19469,15 @@
       </c>
       <c r="D37" s="24" t="n">
         <f aca="false">D35+D36</f>
-        <v>6709.37358154378</v>
+        <v>6693.50490621911</v>
       </c>
       <c r="E37" s="24" t="n">
         <f aca="false">D37-C37</f>
-        <v>276.686299192328</v>
+        <v>260.817623867653</v>
       </c>
       <c r="F37" s="25" t="n">
         <f aca="false">IF(C37=0,"-",D37/C37-1)</f>
-        <v>0.0430125524602194</v>
+        <v>0.040545671259852</v>
       </c>
       <c r="G37" s="27"/>
     </row>
@@ -19289,15 +19494,15 @@
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">D37*입력!D53</f>
-        <v>670.937358154378</v>
+        <v>669.350490621911</v>
       </c>
       <c r="E38" s="17" t="n">
         <f aca="false">D38-C38</f>
-        <v>27.6686299192329</v>
+        <v>26.0817623867654</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">IF(C38=0,"-",D38/C38-1)</f>
-        <v>0.0430125524602196</v>
+        <v>0.0405456712598522</v>
       </c>
       <c r="G38" s="8"/>
     </row>
@@ -19314,15 +19519,15 @@
       </c>
       <c r="D39" s="17" t="n">
         <f aca="false">D37+D38</f>
-        <v>7380.31093969816</v>
+        <v>7362.85539684102</v>
       </c>
       <c r="E39" s="17" t="n">
         <f aca="false">D39-C39</f>
-        <v>304.354929111561</v>
+        <v>286.899386254418</v>
       </c>
       <c r="F39" s="18" t="n">
         <f aca="false">IF(C39=0,"-",D39/C39-1)</f>
-        <v>0.0430125524602194</v>
+        <v>0.040545671259852</v>
       </c>
       <c r="G39" s="8"/>
     </row>
@@ -19363,15 +19568,15 @@
       </c>
       <c r="D41" s="17" t="n">
         <f aca="false">D35/(1-입력!D52)</f>
-        <v>6791.55135291404</v>
+        <v>6775.48831482853</v>
       </c>
       <c r="E41" s="17" t="n">
         <f aca="false">D41-C41</f>
-        <v>280.075209223937</v>
+        <v>264.012171138428</v>
       </c>
       <c r="F41" s="18" t="n">
         <f aca="false">IF(C41=0,"-",D41/C41-1)</f>
-        <v>0.0430125524602194</v>
+        <v>0.040545671259852</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>66</v>
@@ -19390,15 +19595,15 @@
       </c>
       <c r="D42" s="17" t="n">
         <f aca="false">D41-D37</f>
-        <v>82.1777713702595</v>
+        <v>81.9834086094252</v>
       </c>
       <c r="E42" s="17" t="n">
         <f aca="false">D42-C42</f>
-        <v>3.38891003160916</v>
+        <v>3.19454727077482</v>
       </c>
       <c r="F42" s="18" t="n">
         <f aca="false">IF(C42=0,"-",D42/C42-1)</f>
-        <v>0.0430125524602132</v>
+        <v>0.04054567125985</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>68</v>
@@ -19428,11 +19633,11 @@
       </c>
       <c r="D44" s="18" t="n">
         <f aca="false">D20/D37</f>
-        <v>0.778475357739841</v>
+        <v>0.780320933842842</v>
       </c>
       <c r="E44" s="18" t="n">
         <f aca="false">D44-C44</f>
-        <v>-0.0376313472810513</v>
+        <v>-0.0357857711780509</v>
       </c>
       <c r="F44" s="29"/>
       <c r="G44" s="8"/>
@@ -19450,11 +19655,11 @@
       </c>
       <c r="D45" s="18" t="n">
         <f aca="false">D24/D37</f>
-        <v>0.0924839082766227</v>
+        <v>0.0927031651732353</v>
       </c>
       <c r="E45" s="18" t="n">
         <f aca="false">D45-C45</f>
-        <v>0.0201261944590159</v>
+        <v>0.0203454513556285</v>
       </c>
       <c r="F45" s="29"/>
       <c r="G45" s="8"/>
@@ -19472,11 +19677,11 @@
       </c>
       <c r="D46" s="18" t="n">
         <f aca="false">D31/D37</f>
-        <v>0.0119236168664188</v>
+        <v>0.0119518848676229</v>
       </c>
       <c r="E46" s="18" t="n">
         <f aca="false">D46-C46</f>
-        <v>-0.000512865195982395</v>
+        <v>-0.00048459719477824</v>
       </c>
       <c r="F46" s="29"/>
       <c r="G46" s="8"/>
@@ -19494,11 +19699,11 @@
       </c>
       <c r="D47" s="18" t="n">
         <f aca="false">(D35-D34)/D37</f>
-        <v>0.018018018018018</v>
+        <v>0.015924917017201</v>
       </c>
       <c r="E47" s="18" t="n">
         <f aca="false">D47-C47</f>
-        <v>0.018018018018018</v>
+        <v>0.015924917017201</v>
       </c>
       <c r="F47" s="29"/>
       <c r="G47" s="8"/>
@@ -19549,15 +19754,15 @@
       </c>
       <c r="D50" s="30" t="n">
         <f aca="false">D37*입력!D6</f>
-        <v>16773433.9538595</v>
+        <v>16733762.2655478</v>
       </c>
       <c r="E50" s="17" t="n">
         <f aca="false">D50-C50</f>
-        <v>691715.747980822</v>
+        <v>652044.059669133</v>
       </c>
       <c r="F50" s="18" t="n">
         <f aca="false">IF(C50=0,"-",D50/C50-1)</f>
-        <v>0.0430125524602196</v>
+        <v>0.040545671259852</v>
       </c>
       <c r="G50" s="8"/>
     </row>
@@ -19599,15 +19804,15 @@
       </c>
       <c r="D52" s="30" t="n">
         <f aca="false">D37*D51</f>
-        <v>369015546.984908</v>
+        <v>368142769.842051</v>
       </c>
       <c r="E52" s="17" t="n">
         <f aca="false">D52-C52</f>
-        <v>15217746.4555781</v>
+        <v>14344969.312721</v>
       </c>
       <c r="F52" s="18" t="n">
         <f aca="false">IF(C52=0,"-",D52/C52-1)</f>
-        <v>0.0430125524602196</v>
+        <v>0.0405456712598522</v>
       </c>
       <c r="G52" s="8"/>
     </row>
@@ -19624,15 +19829,15 @@
       </c>
       <c r="D53" s="30" t="n">
         <f aca="false">D36*D51</f>
-        <v>36569108.2597657</v>
+        <v>36482616.8311942</v>
       </c>
       <c r="E53" s="17" t="n">
         <f aca="false">D53-C53</f>
-        <v>1508064.9640663</v>
+        <v>1421573.53549488</v>
       </c>
       <c r="F53" s="18" t="n">
         <f aca="false">IF(C53=0,"-",D53/C53-1)</f>
-        <v>0.0430125524602196</v>
+        <v>0.0405456712598524</v>
       </c>
       <c r="G53" s="8"/>
     </row>
@@ -20996,7 +21201,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
         <v>196</v>
       </c>
@@ -22256,7 +22461,7 @@
         <v>45000</v>
       </c>
       <c r="C6" s="71" t="n">
-        <f aca="false">((개당원가분석!$C$34-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A6))/(1-입력!$C$49))*(1+입력!$C$51)</f>
+        <f aca="false">(개당원가분석!$C$35-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A6))*(1+입력!$C$51)</f>
         <v>6547.49940356358</v>
       </c>
       <c r="D6" s="72" t="n">
@@ -22268,12 +22473,12 @@
         <v>45000</v>
       </c>
       <c r="F6" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A6))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6865.55614184063</v>
+        <f aca="false">(개당원가분석!$D$35-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A6))*(1+입력!$D$51)</f>
+        <v>6846.56381531002</v>
       </c>
       <c r="G6" s="72" t="n">
         <f aca="false">F6-개당원가분석!$D$37</f>
-        <v>156.182560296847</v>
+        <v>153.05890909091</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22285,7 +22490,7 @@
         <v>50000</v>
       </c>
       <c r="C7" s="71" t="n">
-        <f aca="false">((개당원가분석!$C$34-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A7))/(1-입력!$C$49))*(1+입력!$C$51)</f>
+        <f aca="false">(개당원가분석!$C$35-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A7))*(1+입력!$C$51)</f>
         <v>6484.35273689691</v>
       </c>
       <c r="D7" s="72" t="n">
@@ -22297,12 +22502,12 @@
         <v>50000</v>
       </c>
       <c r="F7" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A7))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6779.65573367736</v>
+        <f aca="false">(개당원가분석!$D$35-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A7))*(1+입력!$D$51)</f>
+        <v>6762.38141531002</v>
       </c>
       <c r="G7" s="72" t="n">
         <f aca="false">F7-개당원가분석!$D$37</f>
-        <v>70.2821521335809</v>
+        <v>68.8765090909101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22314,7 +22519,7 @@
         <v>55000</v>
       </c>
       <c r="C8" s="71" t="n">
-        <f aca="false">((개당원가분석!$C$34-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A8))/(1-입력!$C$49))*(1+입력!$C$51)</f>
+        <f aca="false">(개당원가분석!$C$35-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A8))*(1+입력!$C$51)</f>
         <v>6432.68728235145</v>
       </c>
       <c r="D8" s="72" t="n">
@@ -22326,8 +22531,8 @@
         <v>55000</v>
       </c>
       <c r="F8" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A8))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6709.37358154378</v>
+        <f aca="false">(개당원가분석!$D$35-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A8))*(1+입력!$D$51)</f>
+        <v>6693.50490621911</v>
       </c>
       <c r="G8" s="72" t="n">
         <f aca="false">F8-개당원가분석!$D$37</f>
@@ -22343,7 +22548,7 @@
         <v>60000</v>
       </c>
       <c r="C9" s="71" t="n">
-        <f aca="false">((개당원가분석!$C$34-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A9))/(1-입력!$C$49))*(1+입력!$C$51)</f>
+        <f aca="false">(개당원가분석!$C$35-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A9))*(1+입력!$C$51)</f>
         <v>6389.63273689691</v>
       </c>
       <c r="D9" s="72" t="n">
@@ -22355,12 +22560,12 @@
         <v>60000</v>
       </c>
       <c r="F9" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A9))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6650.80512143247</v>
+        <f aca="false">(개당원가분석!$D$35-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A9))*(1+입력!$D$51)</f>
+        <v>6636.10781531002</v>
       </c>
       <c r="G9" s="72" t="n">
         <f aca="false">F9-개당원가분석!$D$37</f>
-        <v>-58.5684601113153</v>
+        <v>-57.3970909090895</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22372,7 +22577,7 @@
         <v>65000</v>
       </c>
       <c r="C10" s="71" t="n">
-        <f aca="false">((개당원가분석!$C$34-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A10))/(1-입력!$C$49))*(1+입력!$C$51)</f>
+        <f aca="false">(개당원가분석!$C$35-(CT계산!$C$31+CT계산!$C$32)+CT계산!$C$30/(입력!$C$6*$A10))*(1+입력!$C$51)</f>
         <v>6353.20196766614</v>
       </c>
       <c r="D10" s="72" t="n">
@@ -22384,12 +22589,12 @@
         <v>65000</v>
       </c>
       <c r="F10" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A10))/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6601.24719364597</v>
+        <f aca="false">(개당원가분석!$D$35-(CT계산!$D$31+CT계산!$D$32)+CT계산!$D$30/(입력!$D$6*$A10))*(1+입력!$D$51)</f>
+        <v>6587.54104607925</v>
       </c>
       <c r="G10" s="72" t="n">
         <f aca="false">F10-개당원가분석!$D$37</f>
-        <v>-108.126387897815</v>
+        <v>-105.963860139858</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22455,8 +22660,8 @@
         <v>620.509090909091</v>
       </c>
       <c r="G15" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F15)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6709.37358154378</v>
+        <f aca="false">(개당원가분석!$D$35-(CT계산!$D$31+CT계산!$D$32)+F15)*(1+입력!$D$51)</f>
+        <v>6693.50490621911</v>
       </c>
       <c r="H15" s="78" t="str">
         <f aca="false">IF(C15&gt;=0,"충족","부족")</f>
@@ -22488,8 +22693,8 @@
         <v>620.509090909091</v>
       </c>
       <c r="G16" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F16)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6709.37358154378</v>
+        <f aca="false">(개당원가분석!$D$35-(CT계산!$D$31+CT계산!$D$32)+F16)*(1+입력!$D$51)</f>
+        <v>6693.50490621911</v>
       </c>
       <c r="H16" s="78" t="str">
         <f aca="false">IF(C16&gt;=0,"충족","부족")</f>
@@ -22521,8 +22726,8 @@
         <v>620.509090909091</v>
       </c>
       <c r="G17" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F17)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6709.37358154378</v>
+        <f aca="false">(개당원가분석!$D$35-(CT계산!$D$31+CT계산!$D$32)+F17)*(1+입력!$D$51)</f>
+        <v>6693.50490621911</v>
       </c>
       <c r="H17" s="78" t="str">
         <f aca="false">IF(C17&gt;=0,"충족","부족")</f>
@@ -22554,8 +22759,8 @@
         <v>551.563636363636</v>
       </c>
       <c r="G18" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F18)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6631.28230139536</v>
+        <f aca="false">(개당원가분석!$D$35-(CT계산!$D$31+CT계산!$D$32)+F18)*(1+입력!$D$51)</f>
+        <v>6616.97545167365</v>
       </c>
       <c r="H18" s="78" t="str">
         <f aca="false">IF(C18&gt;=0,"충족","부족")</f>
@@ -22587,8 +22792,8 @@
         <v>551.563636363636</v>
       </c>
       <c r="G19" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-(CT계산!$D$31+CT계산!$D$32)+F19)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6631.28230139536</v>
+        <f aca="false">(개당원가분석!$D$35-(CT계산!$D$31+CT계산!$D$32)+F19)*(1+입력!$D$51)</f>
+        <v>6616.97545167365</v>
       </c>
       <c r="H19" s="78" t="str">
         <f aca="false">IF(C19&gt;=0,"충족","부족")</f>
@@ -22634,12 +22839,12 @@
         <v>120</v>
       </c>
       <c r="C23" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-개당원가분석!$D$17+B23)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6838.49603052337</v>
+        <f aca="false">(개당원가분석!$D$35+(B23-개당원가분석!$D$17)/(1-입력!$D$49))*(1+입력!$D$51)</f>
+        <v>6822.6273551987</v>
       </c>
       <c r="D23" s="72" t="n">
         <f aca="false">C23-개당원가분석!$D$37</f>
-        <v>129.122448979592</v>
+        <v>129.122448979593</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22651,12 +22856,12 @@
         <v>24</v>
       </c>
       <c r="C24" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-개당원가분석!$D$17+B24)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6729.76133664582</v>
+        <f aca="false">(개당원가분석!$D$35+(B24-개당원가분석!$D$17)/(1-입력!$D$49))*(1+입력!$D$51)</f>
+        <v>6713.89266132115</v>
       </c>
       <c r="D24" s="72" t="n">
         <f aca="false">C24-개당원가분석!$D$37</f>
-        <v>20.3877551020414</v>
+        <v>20.3877551020423</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22668,8 +22873,8 @@
         <v>12</v>
       </c>
       <c r="C25" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-개당원가분석!$D$17+B25)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6716.16949991113</v>
+        <f aca="false">(개당원가분석!$D$35+(B25-개당원가분석!$D$17)/(1-입력!$D$49))*(1+입력!$D$51)</f>
+        <v>6700.30082458646</v>
       </c>
       <c r="D25" s="72" t="n">
         <f aca="false">C25-개당원가분석!$D$37</f>
@@ -22685,8 +22890,8 @@
         <v>6</v>
       </c>
       <c r="C26" s="71" t="n">
-        <f aca="false">((개당원가분석!$D$34-개당원가분석!$D$17+B26)/(1-입력!$D$49))*(1+입력!$D$51)</f>
-        <v>6709.37358154378</v>
+        <f aca="false">(개당원가분석!$D$35+(B26-개당원가분석!$D$17)/(1-입력!$D$49))*(1+입력!$D$51)</f>
+        <v>6693.50490621911</v>
       </c>
       <c r="D26" s="72" t="n">
         <f aca="false">C26-개당원가분석!$D$37</f>
